--- a/data/trans_orig/dukeCONF-Edad-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo confidencial (Duke)</t>
+          <t>Puntuación media de la escala de apoyo confidencial (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,85; 31,64</t>
+          <t>30,84; 31,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,34; 32,11</t>
+          <t>31,34; 32,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,39; 31,16</t>
+          <t>30,35; 31,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 33,34</t>
+          <t>32,16; 33,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,46; 31,32</t>
+          <t>30,43; 31,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 31,85</t>
+          <t>31,11; 31,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,61; 31,33</t>
+          <t>30,59; 31,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,01; 32,72</t>
+          <t>30,98; 32,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 31,37</t>
+          <t>30,77; 31,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,31; 31,86</t>
+          <t>31,34; 31,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,62; 31,17</t>
+          <t>30,59; 31,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,85; 32,89</t>
+          <t>31,9; 32,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,74; 31,45</t>
+          <t>30,78; 31,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 31,55</t>
+          <t>30,86; 31,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 30,7</t>
+          <t>30,01; 30,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 31,95</t>
+          <t>30,85; 31,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,88; 30,75</t>
+          <t>29,89; 30,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 31,05</t>
+          <t>30,28; 31,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,32; 30,95</t>
+          <t>30,3; 30,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,49; 33,13</t>
+          <t>31,53; 33,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,51; 31,02</t>
+          <t>30,49; 31,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 31,25</t>
+          <t>30,73; 31,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 30,74</t>
+          <t>30,26; 30,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,42; 32,56</t>
+          <t>31,41; 32,54</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,49; 30,34</t>
+          <t>29,53; 30,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,01; 30,77</t>
+          <t>30,04; 30,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 30,36</t>
+          <t>29,66; 30,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,48; 31,34</t>
+          <t>30,47; 31,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 30,42</t>
+          <t>29,62; 30,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 30,68</t>
+          <t>29,86; 30,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 30,39</t>
+          <t>29,68; 30,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,89; 31,48</t>
+          <t>30,92; 31,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,7; 30,28</t>
+          <t>29,7; 30,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,04; 30,63</t>
+          <t>30,09; 30,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,79; 30,28</t>
+          <t>29,78; 30,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,79; 31,34</t>
+          <t>30,83; 31,34</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 30,27</t>
+          <t>29,27; 30,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,95; 30,78</t>
+          <t>29,97; 30,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,55; 29,37</t>
+          <t>28,56; 29,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,28; 33,56</t>
+          <t>30,28; 33,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,69; 29,67</t>
+          <t>28,67; 29,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 29,99</t>
+          <t>29,14; 29,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,97; 29,74</t>
+          <t>28,96; 29,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,35; 31,35</t>
+          <t>30,38; 31,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,13; 29,83</t>
+          <t>29,12; 29,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 30,28</t>
+          <t>29,69; 30,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 29,43</t>
+          <t>28,88; 29,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 32,75</t>
+          <t>30,46; 32,72</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,81; 29,95</t>
+          <t>28,83; 29,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,17; 31,18</t>
+          <t>30,16; 31,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,66; 29,67</t>
+          <t>28,69; 29,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 30,17</t>
+          <t>29,31; 30,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,85; 28,89</t>
+          <t>27,77; 28,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,94; 29,96</t>
+          <t>28,94; 30,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,1; 29,02</t>
+          <t>28,08; 29,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 29,72</t>
+          <t>28,97; 29,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,46; 29,24</t>
+          <t>28,47; 29,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,73; 30,42</t>
+          <t>29,72; 30,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,53; 29,21</t>
+          <t>28,52; 29,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 29,83</t>
+          <t>29,26; 29,81</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,11; 29,36</t>
+          <t>28,02; 29,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,99; 30,21</t>
+          <t>28,99; 30,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,99; 29,98</t>
+          <t>28,98; 29,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,31; 30,26</t>
+          <t>29,32; 30,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,47; 28,69</t>
+          <t>27,43; 28,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,62; 29,77</t>
+          <t>28,61; 29,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,7; 28,69</t>
+          <t>27,68; 28,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,37; 30,18</t>
+          <t>29,4; 30,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,91; 28,82</t>
+          <t>27,9; 28,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,99; 29,84</t>
+          <t>28,95; 29,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,41; 29,12</t>
+          <t>28,43; 29,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,48; 30,07</t>
+          <t>29,47; 30,09</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,71; 28,32</t>
+          <t>26,61; 28,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,79; 29,33</t>
+          <t>27,81; 29,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,69; 28,84</t>
+          <t>27,69; 28,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,43; 29,56</t>
+          <t>28,38; 29,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,38</t>
+          <t>25,83; 27,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,44; 29,58</t>
+          <t>28,48; 29,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,91; 28,2</t>
+          <t>27,01; 28,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,29; 28,17</t>
+          <t>27,28; 28,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 27,54</t>
+          <t>26,31; 27,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,38; 29,32</t>
+          <t>28,4; 29,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,45; 28,35</t>
+          <t>27,46; 28,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,83; 28,58</t>
+          <t>27,85; 28,58</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1696,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,23</t>
+          <t>29,87; 30,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,39; 30,76</t>
+          <t>30,41; 30,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,82</t>
+          <t>29,51; 29,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,57; 31,96</t>
+          <t>30,57; 31,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 29,52</t>
+          <t>29,16; 29,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,85; 30,19</t>
+          <t>29,86; 30,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,28; 29,61</t>
+          <t>29,29; 29,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 30,78</t>
+          <t>30,24; 30,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,57; 29,83</t>
+          <t>29,56; 29,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,67</t>
+          <t>29,44; 29,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,27</t>
+          <t>30,47; 31,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeCONF-Edad-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,83</t>
+          <t>32,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,01</t>
+          <t>31,82</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,47</t>
+          <t>32,2</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,84; 31,64</t>
+          <t>30,86; 31,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,34; 32,07</t>
+          <t>31,34; 32,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,35; 31,15</t>
+          <t>30,37; 31,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,16; 33,39</t>
+          <t>31,72; 33,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 31,32</t>
+          <t>30,47; 31,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,11; 31,88</t>
+          <t>31,08; 31,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,59; 31,35</t>
+          <t>30,6; 31,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,98; 32,63</t>
+          <t>30,9; 32,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,77; 31,36</t>
+          <t>30,77; 31,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,34; 31,86</t>
+          <t>31,32; 31,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,59; 31,17</t>
+          <t>30,63; 31,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,9; 32,86</t>
+          <t>31,66; 32,63</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,44</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,13</t>
+          <t>31,39</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,81</t>
+          <t>31,27</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 31,46</t>
+          <t>30,77; 31,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 31,53</t>
+          <t>30,85; 31,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 30,69</t>
+          <t>30,03; 30,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 31,89</t>
+          <t>30,52; 31,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,89; 30,79</t>
+          <t>29,96; 30,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 31,04</t>
+          <t>30,29; 31,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 30,94</t>
+          <t>30,33; 30,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 33,21</t>
+          <t>30,92; 31,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,49; 31,03</t>
+          <t>30,51; 31,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,73; 31,24</t>
+          <t>30,68; 31,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 30,7</t>
+          <t>30,26; 30,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,41; 32,54</t>
+          <t>30,86; 31,59</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,91</t>
+          <t>30,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,23</t>
+          <t>31,08</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,07</t>
+          <t>30,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,53; 30,4</t>
+          <t>29,5; 30,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,04; 30,84</t>
+          <t>30,01; 30,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,66; 30,37</t>
+          <t>29,64; 30,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,3</t>
+          <t>30,37; 31,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 30,37</t>
+          <t>29,6; 30,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,86; 30,64</t>
+          <t>29,88; 30,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 30,4</t>
+          <t>29,67; 30,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 31,52</t>
+          <t>30,77; 31,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,7; 30,29</t>
+          <t>29,68; 30,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,09; 30,61</t>
+          <t>30,08; 30,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,78; 30,28</t>
+          <t>29,79; 30,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 31,34</t>
+          <t>30,69; 31,18</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,73</t>
+          <t>30,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,71</t>
+          <t>30,39</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,28</t>
+          <t>30,39</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1136,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 30,24</t>
+          <t>29,31; 30,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 30,79</t>
+          <t>29,99; 30,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 29,39</t>
+          <t>28,54; 29,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,28; 33,44</t>
+          <t>29,94; 30,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 29,63</t>
+          <t>28,67; 29,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 29,98</t>
+          <t>29,11; 29,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 31,48</t>
+          <t>30,05; 30,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,12; 29,86</t>
+          <t>29,12; 29,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 30,28</t>
+          <t>29,72; 30,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,88; 29,45</t>
+          <t>28,88; 29,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,46; 32,72</t>
+          <t>30,1; 30,64</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,74</t>
+          <t>29,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,34</t>
+          <t>29,28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,55</t>
+          <t>29,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,83; 29,92</t>
+          <t>28,81; 29,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,16; 31,14</t>
+          <t>30,11; 31,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,69; 29,64</t>
+          <t>28,64; 29,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,31; 30,2</t>
+          <t>29,11; 30,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,77; 28,86</t>
+          <t>27,8; 28,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,94; 30,03</t>
+          <t>28,97; 30,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,08; 29,03</t>
+          <t>28,05; 29,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,97; 29,7</t>
+          <t>28,91; 29,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,47; 29,28</t>
+          <t>28,47; 29,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 30,44</t>
+          <t>29,72; 30,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,52; 29,19</t>
+          <t>28,52; 29,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,26; 29,81</t>
+          <t>29,12; 29,69</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,77</t>
+          <t>29,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,75</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,79</t>
+          <t>29,76</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,02; 29,31</t>
+          <t>27,99; 29,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,99; 30,17</t>
+          <t>29,0; 30,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,98; 29,99</t>
+          <t>28,94; 29,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,32; 30,25</t>
+          <t>29,26; 30,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,43; 28,71</t>
+          <t>27,46; 28,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,61; 29,8</t>
+          <t>28,58; 29,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,68; 28,68</t>
+          <t>27,65; 28,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,4; 30,24</t>
+          <t>29,3; 30,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,9; 28,78</t>
+          <t>27,92; 28,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,95; 29,8</t>
+          <t>29,0; 29,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,43; 29,14</t>
+          <t>28,42; 29,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,47; 30,09</t>
+          <t>29,44; 30,06</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,98</t>
+          <t>28,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,74</t>
+          <t>27,75</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,23</t>
+          <t>28,22</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,61; 28,38</t>
+          <t>26,69; 28,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,81; 29,37</t>
+          <t>27,77; 29,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,69; 28,83</t>
+          <t>27,66; 28,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,38; 29,5</t>
+          <t>28,35; 29,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 27,36</t>
+          <t>25,73; 27,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 29,52</t>
+          <t>28,47; 29,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,01; 28,26</t>
+          <t>26,99; 28,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,28; 28,17</t>
+          <t>27,27; 28,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,31; 27,53</t>
+          <t>26,27; 27,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,4; 29,32</t>
+          <t>28,41; 29,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,46; 28,36</t>
+          <t>27,42; 28,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,85; 28,58</t>
+          <t>27,84; 28,55</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30,94</t>
+          <t>30,47</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,44</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,69</t>
+          <t>30,33</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1696,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,25</t>
+          <t>29,88; 30,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,41; 30,76</t>
+          <t>30,41; 30,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,83</t>
+          <t>29,49; 29,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,57; 31,86</t>
+          <t>30,27; 30,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,16; 29,53</t>
+          <t>29,14; 29,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,86; 30,2</t>
+          <t>29,85; 30,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,29; 29,61</t>
+          <t>29,28; 29,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,24; 30,75</t>
+          <t>30,02; 30,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,56; 29,83</t>
+          <t>29,55; 29,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,68</t>
+          <t>29,44; 29,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,21</t>
+          <t>30,2; 30,45</t>
         </is>
       </c>
     </row>
